--- a/jpcore-r4b/develop/StructureDefinition-jp-consent.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-consent.xlsx
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-consent.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-consent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev</t>
+    <t>2.0.0-dev-temp</t>
   </si>
   <si>
     <t>Name</t>
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -373,7 +373,7 @@
     <t>IETF language tag</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -805,7 +805,7 @@
     <t>Regulatory policy examples.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-policy</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-policy|4.3.0</t>
   </si>
   <si>
     <t>Consent.verification</t>
@@ -974,7 +974,7 @@
     <t>Detailed codes for the consent action.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-action</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-action|4.3.0</t>
   </si>
   <si>
     <t>Consent.provision.securityLabel</t>
@@ -996,7 +996,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.3.0</t>
   </si>
   <si>
     <t>Consent.provision.purpose</t>
@@ -1032,7 +1032,7 @@
     <t>The class (type) of information a consent rule covers.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-content-class</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-content-class|4.3.0</t>
   </si>
   <si>
     <t>Consent.provision.code</t>
@@ -1098,7 +1098,7 @@
     <t>Consent.provision.data.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.3.0)
 </t>
   </si>
   <si>
@@ -1421,17 +1421,17 @@
   <dimension ref="A1:AN58"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="40.04296875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="40.04296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="34.33203125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="34.33203125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="239.7578125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="205.55078125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1440,26 +1440,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="125.95703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.5703125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="107.984375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="45.0703125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="46.4453125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="29.85546875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="39.8203125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="25.59375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4b/develop/StructureDefinition-jp-consent.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-consent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-consent.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-consent.xlsx
@@ -268,11 +268,11 @@
     <t>A record of a healthcare consumer’s choices or choices made on their behalf by a third party, which permits or denies identified recipient(s) or recipient role(s) to perform one or more actions within a given policy context, for specific purposes and periods of time.</t>
   </si>
   <si>
-    <t>Broadly, there are 3 key areas of consent for patients: Consent around sharing information (aka Privacy Consent Directive - Authorization to Collect, Use, or Disclose information), consent for specific treatment, or kinds of treatment, and general advance care directives.</t>
-  </si>
-  <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}ppc-1:Either a Policy or PolicyRule {policy.exists() or policyRule.exists()}ppc-2:IF Scope=privacy, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='patient-privacy').exists().not()}ppc-3:IF Scope=research, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='research').exists().not()}ppc-4:IF Scope=adr, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='adr').exists().not()}ppc-5:IF Scope=treatment, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='treatment').exists().not()}</t>
+    <t>大まかに、患者には3つの重要な同意領域があります。情報の共有に関する同意（別名プライバシー同意指令 - 情報を収集、使用、または開示する許可）、特定の治療または治療の種類、および一般的な事前ケア指令の同意。 / Broadly, there are 3 key areas of consent for patients: Consent around sharing information (aka Privacy Consent Directive - Authorization to Collect, Use, or Disclose information), consent for specific treatment, or kinds of treatment, and general advance care directives.</t>
+  </si>
+  <si>
+    <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}ppc-1:ポリシーまたはPolicyruleのいずれか / Either a Policy or PolicyRule {policy.exists() or policyRule.exists()}ppc-2:scope =プライバシーの場合、患者がいる必要があります / IF Scope=privacy, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='patient-privacy').exists().not()}ppc-3:scope =研究の場合、患者がいる必要があります / IF Scope=research, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='research').exists().not()}ppc-4:scope = adrの場合、患者がいる必要があります / IF Scope=adr, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='adr').exists().not()}ppc-5:scope =治療の場合、患者がいる必要があります / IF Scope=treatment, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='treatment').exists().not()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -300,13 +300,13 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
-  </si>
-  <si>
-    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
-  </si>
-  <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>このアーティファクトの論理ID / Logical id of this artifact</t>
+  </si>
+  <si>
+    <t>リソースのURLで使用されるリソースの論理ID。割り当てられたら、この値は変更されません。 / The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、IDが作成操作を使用してサーバーに送信されている場合です。 / The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -319,16 +319,16 @@
 </t>
   </si>
   <si>
-    <t>Metadata about the resource</t>
-  </si>
-  <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -339,13 +339,13 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>このコンテンツが作成されたルールのセット / A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>リソースが構築されたときに従った一連のルールへの参照。コンテンツの処理時に理解する必要があります。多くの場合、これは他のプロファイルなどとともに特別なルールを定義する実装ガイドへの参照です。 / A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>このルールセットを主張することは、コンテンツが限られた取引パートナーのセットによってのみ理解されることを制限します。これにより、本質的に長期的にデータの有用性が制限されます。ただし、既存の健康エコシステムは非常に破壊されており、一般的に計算可能な意味でデータを定義、収集、交換する準備ができていません。可能な限り、実装者や仕様ライターはこの要素の使用を避ける必要があります。多くの場合、使用する場合、URLは、これらの特別なルールを他のプロファイル、バリューセットなどとともに叙述(Narative)の一部として定義する実装ガイドへの参照です。 / Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -358,19 +358,19 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+    <t>リソースコンテンツの言語 / Language of the resource content</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。 / The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>言語は、インデックス作成とアクセシビリティをサポートするために提供されます（通常、テキストから音声までのサービスなどのサービスが言語タグを使用します）。叙述(Narative)のHTML言語タグは、叙述(Narative)に適用されます。リソース上の言語タグを使用して、リソース内のデータから生成された他のプレゼンテーションの言語を指定できます。すべてのコンテンツが基本言語である必要はありません。リソース。言語は、叙述(Narative)に自動的に適用されると想定されるべきではありません。言語が指定されている場合、HTMLのDIV要素にも指定されている場合（XML：LangとHTML Lang属性の関係については、HTML5のルールを参照してください）。 / Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>IETF言語タグ / IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
@@ -390,13 +390,13 @@
 </t>
   </si>
   <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>人間の解釈のためのリソースのテキスト概要 / Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>リソースの概要を含み、人間へのリソースの内容を表すために使用できる人間の読み取り可能な叙述(Narative)。叙述(Narative)はすべての構造化されたデータをエンコードする必要はありませんが、人間が叙述(Narative)を読むだけで「臨床的に安全」にするために十分な詳細を含める必要があります。リソースの定義は、臨床的安全を確保するために、叙述(Narative)で表現するコンテンツを定義する場合があります。 / A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>含まれるリソースには叙述(Narative)がありません。含まれていないリソースには叙述(Narative)が必要です。場合によっては、リソースには、追加の個別のデータがほとんどまたはまったくないテキストのみがあります（すべてのMinoccur = 1要素が満たされている限り）。これは、情報がtext blob (バイナリー ラージ オブジェクト)としてキャプチャされるレガシーシステムからのデータ、またはテキストが生またはナレーションされ、エンコードされた情報が後で追加される場合に必要になる場合があります。 / Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
@@ -416,19 +416,19 @@
 </t>
   </si>
   <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>インラインリソースが含まれています / Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>これらのリソースには、それらを含むリソースを除いて独立した存在はありません - 独立して特定することはできず、独自の独立したトランザクションスコープを持つこともできません。 / These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>識別が失われると、コンテンツを適切に識別できる場合は、これを行うべきではありません。含まれるリソースには、メタ要素にプロファイルとタグがある場合がありますが、セキュリティラベルはありません。 / This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+    <t xml:space="preserve">dom-r4b:R4リソース内に新しいR4Bリソースを含めると、インスタンスがR4システムと共有された場合に相互運用性の問題が発生する可能性があります / Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
 </t>
   </si>
   <si>
@@ -446,33 +446,34 @@
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Consent.modifierExtension</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではなく、それを含む要素の理解および/または含有要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>修飾子拡張機能により、安全に無視できる大部分の拡張機能と明確に区別できるように、安全に無視できない拡張機能が可能になります。これにより、実装者が拡張の存在を禁止する必要性を排除することにより、相互運用性が促進されます。詳細については、[修飾子拡張の定義]（拡張性.html＃modifierextension）を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -485,13 +486,13 @@
 </t>
   </si>
   <si>
-    <t>Identifier for this record (external references)</t>
-  </si>
-  <si>
-    <t>Unique identifier for this copy of the Consent Statement.</t>
-  </si>
-  <si>
-    <t>This identifier identifies this copy of the consent. Where this identifier is also used elsewhere as the identifier for a consent record (e.g. a CDA consent document) then the consent details are expected to be the same.</t>
+    <t>このレコードのidentifier（外部参照） / Identifier for this record (external references)</t>
+  </si>
+  <si>
+    <t>同意声明のこのコピーの一意のidentifier。 / Unique identifier for this copy of the Consent Statement.</t>
+  </si>
+  <si>
+    <t>このidentifierは、同意のこのコピーを識別します。このidentifierが同意記録のidentifierとして他の場所でも使用されている場合（例：CDA同意書）、同意の詳細は同じであると予想されます。 / This identifier identifies this copy of the consent. Where this identifier is also used elsewhere as the identifier for a consent record (e.g. a CDA consent document) then the consent details are expected to be the same.</t>
   </si>
   <si>
     <t>Event.identifier</t>
@@ -512,16 +513,16 @@
     <t>Indicates the current state of this consent.</t>
   </si>
   <si>
-    <t>This element is labeled as a modifier because the status contains the codes rejected and entered-in-error that mark the Consent as not currently valid.</t>
-  </si>
-  <si>
-    <t>The Consent Directive that is pointed to might be in various lifecycle states, e.g., a revoked Consent Directive.</t>
+    <t>この要素には、ステータスが拒否され、現在有効ではないと同意をマークするコードを含むコードを含むため、修飾子としてラベル付けされています。 / This element is labeled as a modifier because the status contains the codes rejected and entered-in-error that mark the Consent as not currently valid.</t>
+  </si>
+  <si>
+    <t>指摘されている同意指令は、たとえば取り消された同意指令など、さまざまなライフサイクル状態にある可能性があります。 / The Consent Directive that is pointed to might be in various lifecycle states, e.g., a revoked Consent Directive.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>Indicates the state of the consent.</t>
+    <t>同意の状態を示します。 / Indicates the state of the consent.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/consent-state-codes|4.3.0</t>
@@ -595,7 +596,7 @@
     <t>The patient/healthcare consumer to whom this consent applies.</t>
   </si>
   <si>
-    <t>Commonly, the patient the consent pertains to is the author, but for young and old people, it may be some other person.</t>
+    <t>一般的に、同意が関係する患者は著者ですが、若い人や老人にとっては、他の人かもしれません。 / Commonly, the patient the consent pertains to is the author, but for young and old people, it may be some other person.</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -614,13 +615,13 @@
 </t>
   </si>
   <si>
-    <t>When this Consent was created or indexed</t>
-  </si>
-  <si>
-    <t>When this  Consent was issued / created / indexed.</t>
-  </si>
-  <si>
-    <t>This is not the time of the original consent, but the time that this statement was made or derived.</t>
+    <t>この同意が作成またはインデックス作成されたとき / When this Consent was created or indexed</t>
+  </si>
+  <si>
+    <t>この同意が発行 / 作成 / インデックスされた日時。 / When this  Consent was issued / created / indexed.</t>
+  </si>
+  <si>
+    <t>これは当初の同意の時期ではなく、この声明が作成または導き出された時間です。 / This is not the time of the original consent, but the time that this statement was made or derived.</t>
   </si>
   <si>
     <t>Event.occurrence[x]</t>
@@ -652,7 +653,7 @@
     <t>Either the Grantor, which is the entity responsible for granting the rights listed in a Consent Directive or the Grantee, which is the entity responsible for complying with the Consent Directive, including any obligations or limitations on authorizations and enforcement of prohibitions.</t>
   </si>
   <si>
-    <t>Commonly, the patient the consent pertains to is the consentor, but particularly for young and old people, it may be some other person - e.g. a legal guardian.</t>
+    <t>一般的に、同意が関係する患者は同意者ですが、特に若者や老人にとっては、他の人かもしれません。法的保護者。 / Commonly, the patient the consent pertains to is the consentor, but particularly for young and old people, it may be some other person - e.g. a legal guardian.</t>
   </si>
   <si>
     <t>Event.performer</t>
@@ -697,7 +698,7 @@
     <t>The source on which this consent statement is based. The source might be a scanned original paper form, or a reference to a consent that links back to such a source, a reference to a document repository (e.g. XDS) that stores the original consent document.</t>
   </si>
   <si>
-    <t>The source can be contained inline (Attachment), referenced directly (Consent), referenced in a consent repository (DocumentReference), or simply by an identifier (Identifier), e.g. a CDA document id.</t>
+    <t>ソースは、インライン（添付ファイル）、直接参照（同意）、同意リポジトリ（documentReference）で参照される、または単にidentifier（identifier）によって含めることができます。CDAドキュメントID。 / The source can be contained inline (Attachment), referenced directly (Consent), referenced in a consent repository (DocumentReference), or simply by an identifier (Identifier), e.g. a CDA document id.</t>
   </si>
   <si>
     <t>Field 19 Informational Material Supplied Indicator</t>
@@ -710,13 +711,13 @@
 </t>
   </si>
   <si>
-    <t>Policies covered by this consent</t>
-  </si>
-  <si>
-    <t>The references to the policies that are included in this consent scope. Policies may be organizational, but are often defined jurisdictionally, or in law.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+    <t>この同意の対象となるポリシー / Policies covered by this consent</t>
+  </si>
+  <si>
+    <t>この同意範囲に含まれるポリシーへの参照。ポリシーは組織的かもしれませんが、しばしば管轄区域または法律で定義されます。 / The references to the policies that are included in this consent scope. Policies may be organizational, but are often defined jurisdictionally, or in law.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 </t>
   </si>
   <si>
@@ -727,10 +728,10 @@
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -742,7 +743,7 @@
     <t>Consent.policy.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -755,10 +756,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>認識されていなくても無視できない拡張機能 / Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではなく、それが含まれている要素の理解、および/または含まれる要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
@@ -768,10 +770,10 @@
     <t>Consent.policy.authority</t>
   </si>
   <si>
-    <t>Enforcement source for policy</t>
-  </si>
-  <si>
-    <t>Entity or Organization having regulatory jurisdiction or accountability for  enforcing policies pertaining to Consent Directives.</t>
+    <t>ポリシーの執行ソース / Enforcement source for policy</t>
+  </si>
+  <si>
+    <t>同意指令に関連するポリシーを実施するための規制管轄権または説明責任を持つエンティティまたは組織。 / Entity or Organization having regulatory jurisdiction or accountability for  enforcing policies pertaining to Consent Directives.</t>
   </si>
   <si>
     <t xml:space="preserve">ppc-1
@@ -781,28 +783,28 @@
     <t>Consent.policy.uri</t>
   </si>
   <si>
-    <t>Specific policy covered by this consent</t>
-  </si>
-  <si>
-    <t>This element is for discoverability / documentation and does not modify or qualify the policy rules.</t>
+    <t>この同意によりカバーされている特定のポリシー / Specific policy covered by this consent</t>
+  </si>
+  <si>
+    <t>この要素は、発見可能性 /ドキュメントのためのものであり、ポリシールールを変更または適格にしません。 / This element is for discoverability / documentation and does not modify or qualify the policy rules.</t>
   </si>
   <si>
     <t>Consent.policyRule</t>
   </si>
   <si>
-    <t>Regulation that this consents to</t>
-  </si>
-  <si>
-    <t>A reference to the specific base computable regulation or policy.</t>
-  </si>
-  <si>
-    <t>If the policyRule is absent, computable consent would need to be constructed from the elements of the Consent resource.</t>
-  </si>
-  <si>
-    <t>Might be a unique identifier of a policy set in XACML, or other rules engine.</t>
-  </si>
-  <si>
-    <t>Regulatory policy examples.</t>
+    <t>これが同意する規制 / Regulation that this consents to</t>
+  </si>
+  <si>
+    <t>特定の基本計算可能な規制またはポリシーへの参照。 / A reference to the specific base computable regulation or policy.</t>
+  </si>
+  <si>
+    <t>Policyruleが存在しない場合、同意リソースの要素から計算可能な同意を構築する必要があります。 / If the policyRule is absent, computable consent would need to be constructed from the elements of the Consent resource.</t>
+  </si>
+  <si>
+    <t>XACMLまたはその他のルールエンジンに設定されたポリシーのユニークなidentifierかもしれません。 / Might be a unique identifier of a policy set in XACML, or other rules engine.</t>
+  </si>
+  <si>
+    <t>規制政策の例。 / Regulatory policy examples.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/consent-policy|4.3.0</t>
@@ -833,10 +835,10 @@
 </t>
   </si>
   <si>
-    <t>Has been verified</t>
-  </si>
-  <si>
-    <t>Has the instruction been verified.</t>
+    <t>検証されています / Has been verified</t>
+  </si>
+  <si>
+    <t>命令が検証されています。 / Has the instruction been verified.</t>
   </si>
   <si>
     <t>Consent.verification.verifiedWith</t>
@@ -855,10 +857,10 @@
     <t>Consent.verification.verificationDate</t>
   </si>
   <si>
-    <t>When consent verified</t>
-  </si>
-  <si>
-    <t>Date verification was collected.</t>
+    <t>同意が確認されたとき / When consent verified</t>
+  </si>
+  <si>
+    <t>日付検証が収集されました。 / Date verification was collected.</t>
   </si>
   <si>
     <t>Consent.provision</t>
@@ -888,7 +890,7 @@
     <t>Action stipulated by this rule. The type can be 'permit' or 'deny' to determine if the rule allows or prohibits the specified operations.</t>
   </si>
   <si>
-    <t>How a rule statement is applied, such as adding additional consent or removing consent.</t>
+    <t>追加の同意の追加や同意の削除など、ルールステートメントがどのように適用されるか。 / How a rule statement is applied, such as adding additional consent or removing consent.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/consent-provision-type|4.3.0</t>
@@ -916,7 +918,7 @@
     <t>Who the consent provision rule applies to.</t>
   </si>
   <si>
-    <t>There is no specific actor associated with the exception</t>
+    <t>例外に関連する特定のアクターはありません / There is no specific actor associated with the exception</t>
   </si>
   <si>
     <t>Consent.provision.actor.id</t>
@@ -962,16 +964,16 @@
     <t>A list of actions controlled by this rule, which are controlled by this provision.</t>
   </si>
   <si>
-    <t>Note that this is the direct action (not the grounds for the action covered in the purpose element). At present, the only action in the understood and tested scope of this resource is 'read'.</t>
-  </si>
-  <si>
-    <t>all actions</t>
+    <t>これは直接的なアクションであることに注意してください（目的要素でカバーされているアクションの根拠ではありません）。現在、このリソースの理解とテストされた範囲の唯一のアクションは「読み取り」です。 / Note that this is the direct action (not the grounds for the action covered in the purpose element). At present, the only action in the understood and tested scope of this resource is 'read'.</t>
+  </si>
+  <si>
+    <t>すべてのアクション / all actions</t>
   </si>
   <si>
     <t>example</t>
   </si>
   <si>
-    <t>Detailed codes for the consent action.</t>
+    <t>同意措置の詳細なコード。 / Detailed codes for the consent action.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/consent-action|4.3.0</t>
@@ -984,16 +986,16 @@
 </t>
   </si>
   <si>
-    <t>Security Labels that define affected resources</t>
-  </si>
-  <si>
-    <t>A security label, comprised of 0..* security label fields (Privacy tags), which define which resources are controlled by this exception.</t>
-  </si>
-  <si>
-    <t>If the consent specifies a security label of "R" then it applies to all resources that are labeled "R" or lower. E.g. for Confidentiality, it's a high water mark. For other kinds of security labels, subsumption logic applies. When the purpose of use tag is on the data, access request purpose of use shall not conflict.</t>
-  </si>
-  <si>
-    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+    <t>影響を受けるリソースを定義するセキュリティラベル / Security Labels that define affected resources</t>
+  </si>
+  <si>
+    <t>0 ..*セキュリティラベルフィールド（プライバシータグ）で構成されるセキュリティラベルは、この例外によって制御されるリソースを定義します。 / A security label, comprised of 0..* security label fields (Privacy tags), which define which resources are controlled by this exception.</t>
+  </si>
+  <si>
+    <t>同意が「R」のセキュリティラベルを指定する場合、「R」または低いラベルのあるすべてのリソースに適用されます。例えば。機密性のために、それは高い水マークです。他の種類のセキュリティラベルの場合、包含ロジックが適用されます。タグの使用目的がデータ上にある場合、アクセス要求の使用目的は競合しないでください。 / If the consent specifies a security label of "R" then it applies to all resources that are labeled "R" or lower. E.g. for Confidentiality, it's a high water mark. For other kinds of security labels, subsumption logic applies. When the purpose of use tag is on the data, access request purpose of use shall not conflict.</t>
+  </si>
+  <si>
+    <t>ヘルスケアプライバシーとセキュリティ分類システムからのセキュリティラベル。 / Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/security-labels|4.3.0</t>
@@ -1002,16 +1004,16 @@
     <t>Consent.provision.purpose</t>
   </si>
   <si>
-    <t>Context of activities covered by this rule</t>
-  </si>
-  <si>
-    <t>The context of the activities a user is taking - why the user is accessing the data - that are controlled by this rule.</t>
-  </si>
-  <si>
-    <t>When the purpose of use tag is on the data, access request purpose of use shall not conflict.</t>
-  </si>
-  <si>
-    <t>What purposes of use are controlled by this exception. If more than one label is specified, operations must have all the specified labels.</t>
+    <t>この規則でカバーされている活動のコンテキスト / Context of activities covered by this rule</t>
+  </si>
+  <si>
+    <t>ユーザーが取っているアクティビティのコンテキスト - ユーザーがデータにアクセスしている理由 - このルールによって制御されます。 / The context of the activities a user is taking - why the user is accessing the data - that are controlled by this rule.</t>
+  </si>
+  <si>
+    <t>タグの使用目的がデータ上にある場合、アクセス要求の使用目的は競合しないでください。 / When the purpose of use tag is on the data, access request purpose of use shall not conflict.</t>
+  </si>
+  <si>
+    <t>この例外によって制御される使用目的。複数のラベルが指定されている場合、操作にはすべての指定されたラベルが必要です。 / What purposes of use are controlled by this exception. If more than one label is specified, operations must have all the specified labels.</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-PurposeOfUse</t>
@@ -1026,10 +1028,10 @@
     <t>Actions controlled by this provision.</t>
   </si>
   <si>
-    <t>Multiple types are or'ed together. The intention of the contentType element is that the codes refer to profiles or document types defined in a standard or an implementation guide somewhere.</t>
-  </si>
-  <si>
-    <t>The class (type) of information a consent rule covers.</t>
+    <t>複数のタイプが一緒にORedされます。ContentType要素の意図は、コードが標準または実装ガイドで定義されているプロファイルまたはドキュメントタイプをどこかに指すことです。 / Multiple types are or'ed together. The intention of the contentType element is that the codes refer to profiles or document types defined in a standard or an implementation guide somewhere.</t>
+  </si>
+  <si>
+    <t>同意ルールがカバーする情報のクラス（タイプ）。 / The class (type) of information a consent rule covers.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/consent-content-class|4.3.0</t>
@@ -1041,7 +1043,7 @@
     <t>If this code is found in an instance, then the rule applies.</t>
   </si>
   <si>
-    <t>Typical use of this is a Document code with class = CDA.</t>
+    <t>これの典型的な使用は、class = cdaのドキュメントコードです。 / Typical use of this is a Document code with class = CDA.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/consent-content-code</t>
@@ -1056,7 +1058,7 @@
     <t>The timeframe for data controlled by this provision.</t>
   </si>
   <si>
-    <t>This has a different sense to the Consent.period - that is when the consent agreement holds. This is the time period of the data that is controlled by the agreement.</t>
+    <t>これは、同意に対して異なる感覚を持っています。これは、契約によって制御されるデータの期間です。 / This has a different sense to the Consent.period - that is when the consent agreement holds. This is the time period of the data that is controlled by the agreement.</t>
   </si>
   <si>
     <t>Consent.provision.data</t>
@@ -1068,7 +1070,7 @@
     <t>The resources controlled by this rule, if specific resources are referenced.</t>
   </si>
   <si>
-    <t>all data</t>
+    <t>すべてのデータ / all data</t>
   </si>
   <si>
     <t>Consent.provision.data.id</t>
@@ -1083,13 +1085,13 @@
     <t>Consent.provision.data.meaning</t>
   </si>
   <si>
-    <t>instance | related | dependents | authoredby</t>
-  </si>
-  <si>
-    <t>How the resource reference is interpreted when testing consent restrictions.</t>
-  </si>
-  <si>
-    <t>How a resource reference is interpreted when testing consent restrictions.</t>
+    <t>インスタンス|関連|扶養家族|authoredby / instance | related | dependents | authoredby</t>
+  </si>
+  <si>
+    <t>同意制限をテストするときのリソース参照の解釈方法。 / How the resource reference is interpreted when testing consent restrictions.</t>
+  </si>
+  <si>
+    <t>同意の制限をテストする際のリソース参照の解釈方法。 / How a resource reference is interpreted when testing consent restrictions.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/consent-data-meaning|4.3.0</t>
@@ -1102,19 +1104,19 @@
 </t>
   </si>
   <si>
-    <t>The actual data reference</t>
-  </si>
-  <si>
-    <t>A reference to a specific resource that defines which resources are covered by this consent.</t>
+    <t>実際のデータ参照 / The actual data reference</t>
+  </si>
+  <si>
+    <t>この同意によってカバーされるリソースを定義する特定のリソースへの参照。 / A reference to a specific resource that defines which resources are covered by this consent.</t>
   </si>
   <si>
     <t>Consent.provision.provision</t>
   </si>
   <si>
-    <t>Nested Exception Rules</t>
-  </si>
-  <si>
-    <t>Rules which provide exceptions to the base rule or subrules.</t>
+    <t>ネストされた例外ルール / Nested Exception Rules</t>
+  </si>
+  <si>
+    <t>基本ルールまたはサブルルの例外を提供するルール。 / Rules which provide exceptions to the base rule or subrules.</t>
   </si>
 </sst>
 </file>
@@ -1445,7 +1447,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="107.984375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="163.27734375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="45.0703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
